--- a/A_algoritmos_ordenamiento/inplace/grafica tiempos promedios.xlsx
+++ b/A_algoritmos_ordenamiento/inplace/grafica tiempos promedios.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\posgrado\analisis_algoritmos\t1_ordenamiento\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\posgrado\analisis_algoritmos\A_algoritmos_ordenamiento\inplace\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D0CAC3-D519-45CC-91D5-D9E38D196ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3707F0-A3DB-4C22-B95A-92101D026C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{26D85B6A-7B27-49CC-8DD4-3C39251E35CF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{26D85B6A-7B27-49CC-8DD4-3C39251E35CF}"/>
   </bookViews>
   <sheets>
     <sheet name="grafica de tiempos" sheetId="1" r:id="rId1"/>
     <sheet name="grafica de timepo (buscar str)" sheetId="2" r:id="rId2"/>
-    <sheet name="permutation sort" sheetId="3" r:id="rId3"/>
-    <sheet name="fibonacci" sheetId="4" r:id="rId4"/>
+    <sheet name="grafica str nueva" sheetId="5" r:id="rId3"/>
+    <sheet name="permutation sort" sheetId="3" r:id="rId4"/>
+    <sheet name="fibonacci" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -183,7 +184,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout>
         <c:manualLayout>
@@ -206,68 +207,23 @@
             <c:v>B. Logico</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="9525" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="2"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="0.12633961106598832"/>
-                  <c:y val="-4.026759832901642E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="es-MX"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>'grafica de tiempos'!$A$2:$A$101</c:f>
@@ -900,68 +856,23 @@
             <c:v>B. Fisico</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="9525" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="2"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="0.13001830949034673"/>
-                  <c:y val="6.0069447665733133E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="es-MX"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>'grafica de tiempos'!$A$2:$A$101</c:f>
@@ -1588,713 +1499,25 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:v>in-place</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="2"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="0.13093798409643637"/>
-                  <c:y val="-2.0537934100333995E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="es-MX"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'grafica de tiempos'!$A$2:$A$101</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="100"/>
-                <c:pt idx="0">
-                  <c:v>1000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7000</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8000</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11000</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12000</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13000</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14000</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17000</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18000</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19000</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20000</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21000</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22000</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23000</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24000</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25000</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26000</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>27000</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28000</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29000</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30000</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>31000</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>32000</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>33000</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>34000</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>35000</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>36000</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>37000</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>38000</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>39000</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>40000</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>41000</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>42000</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>43000</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>44000</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>45000</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>46000</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>47000</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>48000</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>49000</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>50000</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>51000</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>52000</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>53000</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>54000</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>55000</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>56000</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>57000</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>58000</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>59000</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>60000</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>61000</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>62000</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>63000</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>64000</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>65000</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>66000</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>67000</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>68000</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>69000</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>70000</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>71000</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>72000</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>73000</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>74000</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>75000</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>76000</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>77000</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>78000</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>79000</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>80000</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>81000</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>82000</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>83000</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>84000</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>85000</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>86000</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>87000</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>88000</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>89000</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>90000</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>91000</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>92000</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>93000</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>94000</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>95000</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>96000</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>97000</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>98000</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>99000</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>100000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'grafica de tiempos'!$D$2:$D$101</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="100"/>
-                <c:pt idx="0">
-                  <c:v>1E-3</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.1070000000000004E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.4289999999999999E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.6107E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2.5464000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3.7213999999999997E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>5.0106999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>6.9320999999999994E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>8.1892999999999994E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.10217900000000001</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.12235699999999999</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.148893</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.17285700000000001</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.20028599999999999</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.230071</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.267571</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.293929</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.331536</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.36689300000000002</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.41121400000000002</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.44903599999999999</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.50232100000000002</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.55574999999999997</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.65546400000000005</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.87775000000000003</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.76714300000000002</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.74424999999999997</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.80142899999999995</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.84824999999999995</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.91153600000000001</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.97950000000000004</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1.0386070000000001</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1.1107499999999999</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1.1713210000000001</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1.244607</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>1.318786</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1.3918569999999999</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1.471929</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1.5485</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>1.6202859999999999</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>1.714107</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>1.792786</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1.9748570000000001</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>2.0203929999999999</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>2.0606070000000001</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>2.1612140000000002</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>2.2533569999999998</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>2.347893</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>2.433964</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>2.5331070000000002</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>2.6406070000000001</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>2.7436069999999999</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>2.8647499999999999</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>3.0020359999999999</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>3.1186790000000002</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>3.1882860000000002</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>3.2940710000000002</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>3.417964</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>3.5402499999999999</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>3.6404999999999998</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>3.7740360000000002</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>3.899607</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>4.0238209999999999</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>4.1467859999999996</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>4.2737499999999997</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>4.4194290000000001</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>4.5419999999999998</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>4.7101430000000004</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>4.9122139999999996</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>5.0175710000000002</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>5.1649289999999999</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>5.3083210000000003</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>5.5288570000000004</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>5.5947139999999997</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>5.7273569999999996</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>5.8942139999999998</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>6.0562860000000001</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>6.2358929999999999</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>6.3881069999999998</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>6.519857</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>7.1028209999999996</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>6.8485360000000002</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>6.9903930000000001</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>7.1351069999999996</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>7.3174640000000002</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>7.4979639999999996</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>7.6812500000000004</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>7.8457140000000001</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>8.0325000000000006</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>8.2146430000000006</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>8.3983209999999993</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>8.5908569999999997</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>8.7925360000000001</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>8.9842139999999997</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>9.1925000000000008</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>9.4013209999999994</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>9.6188570000000002</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>9.8429640000000003</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>10.071429</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>10.312856999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-D5D8-4CF4-8EEC-5D518DE33C9C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
           <c:idx val="4"/>
           <c:order val="3"/>
           <c:tx>
             <c:v>Bubble sort</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="9525" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent5"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
@@ -2931,13 +2154,19 @@
             <c:v>merge-sort</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="9525" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent4"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
@@ -3577,6 +2806,673 @@
         </c:dLbls>
         <c:axId val="661351592"/>
         <c:axId val="661348968"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:v>in-place</c:v>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="9525" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst>
+                    <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                      <a:srgbClr val="000000">
+                        <a:alpha val="63000"/>
+                      </a:srgbClr>
+                    </a:outerShdw>
+                  </a:effectLst>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'grafica de tiempos'!$A$2:$A$101</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="100"/>
+                      <c:pt idx="0">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>6000</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>9000</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>11000</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>13000</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>14000</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>15000</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>16000</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>17000</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>18000</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>19000</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>20000</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>21000</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>22000</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>23000</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>24000</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>25000</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>26000</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>27000</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>28000</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>29000</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>30000</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>31000</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>32000</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>33000</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>34000</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>35000</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>36000</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>37000</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>38000</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>39000</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>40000</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>41000</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>42000</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>43000</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>44000</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>45000</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>46000</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>47000</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>48000</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>49000</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>50000</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>51000</c:v>
+                      </c:pt>
+                      <c:pt idx="51">
+                        <c:v>52000</c:v>
+                      </c:pt>
+                      <c:pt idx="52">
+                        <c:v>53000</c:v>
+                      </c:pt>
+                      <c:pt idx="53">
+                        <c:v>54000</c:v>
+                      </c:pt>
+                      <c:pt idx="54">
+                        <c:v>55000</c:v>
+                      </c:pt>
+                      <c:pt idx="55">
+                        <c:v>56000</c:v>
+                      </c:pt>
+                      <c:pt idx="56">
+                        <c:v>57000</c:v>
+                      </c:pt>
+                      <c:pt idx="57">
+                        <c:v>58000</c:v>
+                      </c:pt>
+                      <c:pt idx="58">
+                        <c:v>59000</c:v>
+                      </c:pt>
+                      <c:pt idx="59">
+                        <c:v>60000</c:v>
+                      </c:pt>
+                      <c:pt idx="60">
+                        <c:v>61000</c:v>
+                      </c:pt>
+                      <c:pt idx="61">
+                        <c:v>62000</c:v>
+                      </c:pt>
+                      <c:pt idx="62">
+                        <c:v>63000</c:v>
+                      </c:pt>
+                      <c:pt idx="63">
+                        <c:v>64000</c:v>
+                      </c:pt>
+                      <c:pt idx="64">
+                        <c:v>65000</c:v>
+                      </c:pt>
+                      <c:pt idx="65">
+                        <c:v>66000</c:v>
+                      </c:pt>
+                      <c:pt idx="66">
+                        <c:v>67000</c:v>
+                      </c:pt>
+                      <c:pt idx="67">
+                        <c:v>68000</c:v>
+                      </c:pt>
+                      <c:pt idx="68">
+                        <c:v>69000</c:v>
+                      </c:pt>
+                      <c:pt idx="69">
+                        <c:v>70000</c:v>
+                      </c:pt>
+                      <c:pt idx="70">
+                        <c:v>71000</c:v>
+                      </c:pt>
+                      <c:pt idx="71">
+                        <c:v>72000</c:v>
+                      </c:pt>
+                      <c:pt idx="72">
+                        <c:v>73000</c:v>
+                      </c:pt>
+                      <c:pt idx="73">
+                        <c:v>74000</c:v>
+                      </c:pt>
+                      <c:pt idx="74">
+                        <c:v>75000</c:v>
+                      </c:pt>
+                      <c:pt idx="75">
+                        <c:v>76000</c:v>
+                      </c:pt>
+                      <c:pt idx="76">
+                        <c:v>77000</c:v>
+                      </c:pt>
+                      <c:pt idx="77">
+                        <c:v>78000</c:v>
+                      </c:pt>
+                      <c:pt idx="78">
+                        <c:v>79000</c:v>
+                      </c:pt>
+                      <c:pt idx="79">
+                        <c:v>80000</c:v>
+                      </c:pt>
+                      <c:pt idx="80">
+                        <c:v>81000</c:v>
+                      </c:pt>
+                      <c:pt idx="81">
+                        <c:v>82000</c:v>
+                      </c:pt>
+                      <c:pt idx="82">
+                        <c:v>83000</c:v>
+                      </c:pt>
+                      <c:pt idx="83">
+                        <c:v>84000</c:v>
+                      </c:pt>
+                      <c:pt idx="84">
+                        <c:v>85000</c:v>
+                      </c:pt>
+                      <c:pt idx="85">
+                        <c:v>86000</c:v>
+                      </c:pt>
+                      <c:pt idx="86">
+                        <c:v>87000</c:v>
+                      </c:pt>
+                      <c:pt idx="87">
+                        <c:v>88000</c:v>
+                      </c:pt>
+                      <c:pt idx="88">
+                        <c:v>89000</c:v>
+                      </c:pt>
+                      <c:pt idx="89">
+                        <c:v>90000</c:v>
+                      </c:pt>
+                      <c:pt idx="90">
+                        <c:v>91000</c:v>
+                      </c:pt>
+                      <c:pt idx="91">
+                        <c:v>92000</c:v>
+                      </c:pt>
+                      <c:pt idx="92">
+                        <c:v>93000</c:v>
+                      </c:pt>
+                      <c:pt idx="93">
+                        <c:v>94000</c:v>
+                      </c:pt>
+                      <c:pt idx="94">
+                        <c:v>95000</c:v>
+                      </c:pt>
+                      <c:pt idx="95">
+                        <c:v>96000</c:v>
+                      </c:pt>
+                      <c:pt idx="96">
+                        <c:v>97000</c:v>
+                      </c:pt>
+                      <c:pt idx="97">
+                        <c:v>98000</c:v>
+                      </c:pt>
+                      <c:pt idx="98">
+                        <c:v>99000</c:v>
+                      </c:pt>
+                      <c:pt idx="99">
+                        <c:v>100000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'grafica de tiempos'!$D$2:$D$101</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="100"/>
+                      <c:pt idx="0">
+                        <c:v>1E-3</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>4.1070000000000004E-3</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>9.4289999999999999E-3</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1.6107E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>2.5464000000000001E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>3.7213999999999997E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>5.0106999999999999E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>6.9320999999999994E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>8.1892999999999994E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>0.10217900000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>0.12235699999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>0.148893</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>0.17285700000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>0.20028599999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>0.230071</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>0.267571</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>0.293929</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>0.331536</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>0.36689300000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>0.41121400000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>0.44903599999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>0.50232100000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>0.55574999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>0.65546400000000005</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>0.87775000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>0.76714300000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>0.74424999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>0.80142899999999995</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>0.84824999999999995</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>0.91153600000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>0.97950000000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>1.0386070000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>1.1107499999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>1.1713210000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>1.244607</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>1.318786</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>1.3918569999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>1.471929</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>1.5485</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>1.6202859999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>1.714107</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>1.792786</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>1.9748570000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>2.0203929999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>2.0606070000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="45">
+                        <c:v>2.1612140000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="46">
+                        <c:v>2.2533569999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="47">
+                        <c:v>2.347893</c:v>
+                      </c:pt>
+                      <c:pt idx="48">
+                        <c:v>2.433964</c:v>
+                      </c:pt>
+                      <c:pt idx="49">
+                        <c:v>2.5331070000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="50">
+                        <c:v>2.6406070000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="51">
+                        <c:v>2.7436069999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="52">
+                        <c:v>2.8647499999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="53">
+                        <c:v>3.0020359999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="54">
+                        <c:v>3.1186790000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="55">
+                        <c:v>3.1882860000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="56">
+                        <c:v>3.2940710000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="57">
+                        <c:v>3.417964</c:v>
+                      </c:pt>
+                      <c:pt idx="58">
+                        <c:v>3.5402499999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="59">
+                        <c:v>3.6404999999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="60">
+                        <c:v>3.7740360000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="61">
+                        <c:v>3.899607</c:v>
+                      </c:pt>
+                      <c:pt idx="62">
+                        <c:v>4.0238209999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="63">
+                        <c:v>4.1467859999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="64">
+                        <c:v>4.2737499999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="65">
+                        <c:v>4.4194290000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="66">
+                        <c:v>4.5419999999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="67">
+                        <c:v>4.7101430000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="68">
+                        <c:v>4.9122139999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="69">
+                        <c:v>5.0175710000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="70">
+                        <c:v>5.1649289999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="71">
+                        <c:v>5.3083210000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="72">
+                        <c:v>5.5288570000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="73">
+                        <c:v>5.5947139999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="74">
+                        <c:v>5.7273569999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="75">
+                        <c:v>5.8942139999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="76">
+                        <c:v>6.0562860000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="77">
+                        <c:v>6.2358929999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="78">
+                        <c:v>6.3881069999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="79">
+                        <c:v>6.519857</c:v>
+                      </c:pt>
+                      <c:pt idx="80">
+                        <c:v>7.1028209999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="81">
+                        <c:v>6.8485360000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="82">
+                        <c:v>6.9903930000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="83">
+                        <c:v>7.1351069999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="84">
+                        <c:v>7.3174640000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="85">
+                        <c:v>7.4979639999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="86">
+                        <c:v>7.6812500000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="87">
+                        <c:v>7.8457140000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="88">
+                        <c:v>8.0325000000000006</c:v>
+                      </c:pt>
+                      <c:pt idx="89">
+                        <c:v>8.2146430000000006</c:v>
+                      </c:pt>
+                      <c:pt idx="90">
+                        <c:v>8.3983209999999993</c:v>
+                      </c:pt>
+                      <c:pt idx="91">
+                        <c:v>8.5908569999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="92">
+                        <c:v>8.7925360000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="93">
+                        <c:v>8.9842139999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="94">
+                        <c:v>9.1925000000000008</c:v>
+                      </c:pt>
+                      <c:pt idx="95">
+                        <c:v>9.4013209999999994</c:v>
+                      </c:pt>
+                      <c:pt idx="96">
+                        <c:v>9.6188570000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="97">
+                        <c:v>9.8429640000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="98">
+                        <c:v>10.071429</c:v>
+                      </c:pt>
+                      <c:pt idx="99">
+                        <c:v>10.312856999999999</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-D5D8-4CF4-8EEC-5D518DE33C9C}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+          </c:ext>
+        </c:extLst>
       </c:scatterChart>
       <c:valAx>
         <c:axId val="661351592"/>
@@ -3589,9 +3485,9 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -3599,6 +3495,35 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-MX"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3607,12 +3532,10 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
               </a:schemeClr>
             </a:solidFill>
-            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -3623,9 +3546,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -3651,9 +3573,9 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -3661,6 +3583,35 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-MX"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3669,12 +3620,10 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
               </a:schemeClr>
             </a:solidFill>
-            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -3685,9 +3634,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -3704,61 +3652,33 @@
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
+        <a:ln>
+          <a:noFill/>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="l"/>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="4.7982752203012832E-2"/>
-          <c:y val="3.7970626142331335E-2"/>
-          <c:w val="0.18708051928974648"/>
-          <c:h val="0.26914605903774008"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="1"/>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
       <c:spPr>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
+        <a:noFill/>
         <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
+          <a:noFill/>
         </a:ln>
-        <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-            <a:schemeClr val="tx1"/>
-          </a:outerShdw>
-        </a:effectLst>
+        <a:effectLst/>
       </c:spPr>
       <c:txPr>
         <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:effectLst>
-                <a:outerShdw blurRad="50800" dist="50800" dir="5400000" sx="1000" sy="1000" algn="ctr" rotWithShape="0">
-                  <a:srgbClr val="000000">
-                    <a:alpha val="43137"/>
-                  </a:srgbClr>
-                </a:outerShdw>
-              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
@@ -3780,17 +3700,28 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
@@ -4696,14 +4627,912 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
+      <c14:style val="106"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="2"/>
+      <c:style val="6"/>
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:forward val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:forward val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:forward val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:forward val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'grafica str nueva'!$B$1:$B$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>260</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>270</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>280</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>290</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>310</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>330</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>340</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>380</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>390</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>410</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>430</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>440</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>460</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>470</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>490</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>510</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>520</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>530</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>540</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>560</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>570</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>580</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>590</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>610</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>620</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>630</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>660</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>670</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>680</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>690</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>710</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>720</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>730</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>740</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>760</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>770</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>780</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>790</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>810</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>820</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>830</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>840</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>860</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>870</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>880</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>890</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>910</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>920</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>930</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>940</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>960</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>970</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>980</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>990</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>1000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'grafica str nueva'!$A$1:$A$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>1.8929999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.679E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.6429999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.6429999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1535999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.3036000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.5070999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.6607E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.8856999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.0929E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.2464000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.4785999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.6356999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.9642999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.0536000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.2679E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.4393E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.6499999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.875E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.0429E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4.2535999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.4357000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.65E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.7821000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5.0535999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5.3499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5.4642999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>5.6929E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5.8820999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5.9429000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6.1463999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>6.4429E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>6.9142999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>6.9892999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7.3214000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7.2892999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7.4714000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7.5320999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7.6356999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7.8214000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8.0321000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8.1963999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8.4036E-2</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8.5892999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8.8070999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8.9820999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>9.1786000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>9.3606999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>9.5713999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>9.7392999999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>9.9500000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.101393</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.103214</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.105214</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.10685699999999999</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.109071</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.110821</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.113714</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.11799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.116893</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.118571</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.120321</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.122321</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.12428599999999999</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.12625</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.12853600000000001</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.13017899999999999</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.13339300000000001</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.133857</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.135821</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.13778599999999999</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.13964299999999999</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.14146400000000001</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.14349999999999999</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.146786</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.15082100000000001</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.14907100000000001</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.15142900000000001</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.15296399999999999</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.155</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.156857</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.15882099999999999</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.16042899999999999</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.16275000000000001</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.165571</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.16650000000000001</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.16839299999999999</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.16989299999999999</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.17446400000000001</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.17574999999999999</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.17589299999999999</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.17760699999999999</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.17982100000000001</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.18132100000000001</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.183786</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.18496399999999999</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.18732099999999999</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.18907099999999999</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.19078600000000001</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.193214</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6AFA-47F3-862A-1CEF0855C624}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="572093832"/>
+        <c:axId val="572094160"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="572093832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="572094160"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="572094160"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="572093832"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="6"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4717,13 +5546,148 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-MX"/>
+              <a:t>Permutation sort</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
@@ -4743,27 +5707,63 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="9525" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="6"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
+                <a:round/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
           </c:marker>
           <c:xVal>
@@ -4885,9 +5885,9 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -4903,12 +5903,10 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
               </a:schemeClr>
             </a:solidFill>
-            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -4919,9 +5917,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -4947,9 +5944,9 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -4965,12 +5962,10 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
               </a:schemeClr>
             </a:solidFill>
-            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -4981,9 +5976,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -5018,17 +6012,28 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
@@ -5050,7 +6055,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="es-ES"/>
@@ -5317,42 +6322,8 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="17">
   <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -5396,7 +6367,549 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="248">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5912,63 +7425,67 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="248">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:chartArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
     </cs:spPr>
     <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
@@ -5977,9 +7494,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
+      <a:schemeClr val="lt1">
         <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -5998,14 +7514,6 @@
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -6014,20 +7522,20 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
@@ -6036,13 +7544,13 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="9525" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -6054,30 +7562,31 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -6093,21 +7602,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -6126,14 +7632,13 @@
           <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -6145,14 +7650,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -6166,9 +7671,8 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -6182,12 +7686,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
@@ -6199,9 +7697,9 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -6216,14 +7714,13 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -6235,14 +7732,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -6254,14 +7751,13 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -6270,14 +7766,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -6285,7 +7780,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea3D>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -6298,11 +7793,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -6310,14 +7813,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -6329,12 +7832,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -6350,7 +7860,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
+        <a:prstDash val="sysDash"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -6359,9 +7869,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -6377,14 +7886,13 @@
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -6393,20 +7901,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -6418,73 +7923,71 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="248">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:chartArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
     </cs:spPr>
     <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
@@ -6493,9 +7996,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
+      <a:schemeClr val="lt1">
         <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -6514,14 +8016,6 @@
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -6530,20 +8024,20 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
@@ -6552,13 +8046,13 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="9525" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -6570,30 +8064,31 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -6609,21 +8104,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -6642,14 +8134,13 @@
           <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -6661,14 +8152,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -6682,9 +8173,8 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -6698,12 +8188,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
@@ -6715,9 +8199,9 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -6732,14 +8216,13 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -6751,14 +8234,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -6770,14 +8253,13 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -6786,14 +8268,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -6801,7 +8282,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea3D>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -6814,11 +8295,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -6826,14 +8315,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -6845,12 +8334,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -6866,7 +8362,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
+        <a:prstDash val="sysDash"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -6875,9 +8371,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -6893,14 +8388,13 @@
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -6909,20 +8403,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -6934,17 +8425,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7533,16 +9018,59 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>8573</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{626F269C-7D50-4DC8-8685-0E89D6BCB9AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>502920</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>4761</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>28574</xdr:rowOff>
+      <xdr:colOff>441959</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7570,7 +9098,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -7909,16 +9437,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE79BB4-E254-4B65-802D-7ABD6D91CD15}">
   <dimension ref="A1:I101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" customWidth="1"/>
     <col min="7" max="7" width="14" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -7936,7 +9464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1000</v>
       </c>
@@ -7956,7 +9484,7 @@
         <v>1.07E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2000</v>
       </c>
@@ -7977,7 +9505,7 @@
       </c>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3000</v>
       </c>
@@ -7997,7 +9525,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4000</v>
       </c>
@@ -8017,7 +9545,7 @@
         <v>7.1400000000000001E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5000</v>
       </c>
@@ -8037,7 +9565,7 @@
         <v>8.5700000000000001E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6000</v>
       </c>
@@ -8057,7 +9585,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7000</v>
       </c>
@@ -8077,7 +9605,7 @@
         <v>1.3209999999999999E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8000</v>
       </c>
@@ -8097,7 +9625,7 @@
         <v>1.5E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9000</v>
       </c>
@@ -8117,7 +9645,7 @@
         <v>1.6789999999999999E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10000</v>
       </c>
@@ -8137,7 +9665,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11000</v>
       </c>
@@ -8157,7 +9685,7 @@
         <v>2.1069999999999999E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12000</v>
       </c>
@@ -8177,7 +9705,7 @@
         <v>2.2499999999999998E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13000</v>
       </c>
@@ -8197,7 +9725,7 @@
         <v>2.5360000000000001E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14000</v>
       </c>
@@ -8217,7 +9745,7 @@
         <v>2.643E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15000</v>
       </c>
@@ -8237,7 +9765,7 @@
         <v>2.8930000000000002E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16000</v>
       </c>
@@ -8257,7 +9785,7 @@
         <v>3.0360000000000001E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17000</v>
       </c>
@@ -8277,7 +9805,7 @@
         <v>3.2139999999999998E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18000</v>
       </c>
@@ -8297,7 +9825,7 @@
         <v>3.5360000000000001E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19000</v>
       </c>
@@ -8317,7 +9845,7 @@
         <v>3.679E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20000</v>
       </c>
@@ -8337,7 +9865,7 @@
         <v>3.9639999999999996E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21000</v>
       </c>
@@ -8357,7 +9885,7 @@
         <v>4.0359999999999997E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22000</v>
       </c>
@@ -8377,7 +9905,7 @@
         <v>4.4289999999999998E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23000</v>
       </c>
@@ -8397,7 +9925,7 @@
         <v>4.5360000000000001E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24000</v>
       </c>
@@ -8417,7 +9945,7 @@
         <v>4.7499999999999999E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25000</v>
       </c>
@@ -8437,7 +9965,7 @@
         <v>4.9290000000000002E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26000</v>
       </c>
@@ -8457,7 +9985,7 @@
         <v>5.2139999999999999E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27000</v>
       </c>
@@ -8477,7 +10005,7 @@
         <v>5.2500000000000003E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28000</v>
       </c>
@@ -8497,7 +10025,7 @@
         <v>5.6429999999999996E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29000</v>
       </c>
@@ -8517,7 +10045,7 @@
         <v>5.679E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30000</v>
       </c>
@@ -8537,7 +10065,7 @@
         <v>5.9290000000000002E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31000</v>
       </c>
@@ -8557,7 +10085,7 @@
         <v>6.1069999999999996E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32000</v>
       </c>
@@ -8577,7 +10105,7 @@
         <v>6.3569999999999998E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33000</v>
       </c>
@@ -8597,7 +10125,7 @@
         <v>6.7140000000000003E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34000</v>
       </c>
@@ -8617,7 +10145,7 @@
         <v>6.8209999999999998E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35000</v>
       </c>
@@ -8637,7 +10165,7 @@
         <v>7.143E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36000</v>
       </c>
@@ -8657,7 +10185,7 @@
         <v>7.3569999999999998E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37000</v>
       </c>
@@ -8677,7 +10205,7 @@
         <v>7.3930000000000003E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38000</v>
       </c>
@@ -8697,7 +10225,7 @@
         <v>7.6790000000000001E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39000</v>
       </c>
@@ -8717,7 +10245,7 @@
         <v>7.8930000000000007E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40000</v>
       </c>
@@ -8737,7 +10265,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41000</v>
       </c>
@@ -8757,7 +10285,7 @@
         <v>8.2500000000000004E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42000</v>
       </c>
@@ -8777,7 +10305,7 @@
         <v>8.3929999999999994E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43000</v>
       </c>
@@ -8797,7 +10325,7 @@
         <v>8.6789999999999992E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44000</v>
       </c>
@@ -8817,7 +10345,7 @@
         <v>8.8570000000000003E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45000</v>
       </c>
@@ -8837,7 +10365,7 @@
         <v>9.1070000000000005E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46000</v>
       </c>
@@ -8857,7 +10385,7 @@
         <v>9.4640000000000002E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47000</v>
       </c>
@@ -8877,7 +10405,7 @@
         <v>9.5709999999999996E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48000</v>
       </c>
@@ -8897,7 +10425,7 @@
         <v>9.6790000000000001E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49000</v>
       </c>
@@ -8917,7 +10445,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50000</v>
       </c>
@@ -8937,7 +10465,7 @@
         <v>1.0357E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51000</v>
       </c>
@@ -8957,7 +10485,7 @@
         <v>1.0286E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52000</v>
       </c>
@@ -8977,7 +10505,7 @@
         <v>1.0714E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53000</v>
       </c>
@@ -8997,7 +10525,7 @@
         <v>1.0928999999999999E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54000</v>
       </c>
@@ -9017,7 +10545,7 @@
         <v>1.1214E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55000</v>
       </c>
@@ -9037,7 +10565,7 @@
         <v>1.1179E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56000</v>
       </c>
@@ -9057,7 +10585,7 @@
         <v>1.1464E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57000</v>
       </c>
@@ -9077,7 +10605,7 @@
         <v>1.1856999999999999E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58000</v>
       </c>
@@ -9097,7 +10625,7 @@
         <v>1.2107E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59000</v>
       </c>
@@ -9117,7 +10645,7 @@
         <v>1.2071E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60000</v>
       </c>
@@ -9137,7 +10665,7 @@
         <v>1.2321E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61000</v>
       </c>
@@ -9157,7 +10685,7 @@
         <v>1.2463999999999999E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62000</v>
       </c>
@@ -9177,7 +10705,7 @@
         <v>1.2857E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63000</v>
       </c>
@@ -9197,7 +10725,7 @@
         <v>1.2964E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64000</v>
       </c>
@@ -9217,7 +10745,7 @@
         <v>1.3285999999999999E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65000</v>
       </c>
@@ -9237,7 +10765,7 @@
         <v>1.35E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66000</v>
       </c>
@@ -9257,7 +10785,7 @@
         <v>1.3571E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67000</v>
       </c>
@@ -9277,7 +10805,7 @@
         <v>1.3964000000000001E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68000</v>
       </c>
@@ -9297,7 +10825,7 @@
         <v>1.4071E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69000</v>
       </c>
@@ -9317,7 +10845,7 @@
         <v>1.4357E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70000</v>
       </c>
@@ -9337,7 +10865,7 @@
         <v>1.4571000000000001E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71000</v>
       </c>
@@ -9357,7 +10885,7 @@
         <v>1.5070999999999999E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72000</v>
       </c>
@@ -9377,7 +10905,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73000</v>
       </c>
@@ -9397,7 +10925,7 @@
         <v>1.5143E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74000</v>
       </c>
@@ -9417,7 +10945,7 @@
         <v>1.55E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75000</v>
       </c>
@@ -9437,7 +10965,7 @@
         <v>1.5821000000000002E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76000</v>
       </c>
@@ -9457,7 +10985,7 @@
         <v>1.5928999999999999E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77000</v>
       </c>
@@ -9477,7 +11005,7 @@
         <v>1.6285999999999998E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78000</v>
       </c>
@@ -9497,7 +11025,7 @@
         <v>1.6500000000000001E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79000</v>
       </c>
@@ -9517,7 +11045,7 @@
         <v>1.6607E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80000</v>
       </c>
@@ -9537,7 +11065,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81000</v>
       </c>
@@ -9557,7 +11085,7 @@
         <v>1.7107000000000001E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82000</v>
       </c>
@@ -9577,7 +11105,7 @@
         <v>1.7464E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83000</v>
       </c>
@@ -9597,7 +11125,7 @@
         <v>1.7464E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84000</v>
       </c>
@@ -9617,7 +11145,7 @@
         <v>1.7821E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85000</v>
       </c>
@@ -9637,7 +11165,7 @@
         <v>1.8142999999999999E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86000</v>
       </c>
@@ -9657,7 +11185,7 @@
         <v>1.8214000000000001E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87000</v>
       </c>
@@ -9677,7 +11205,7 @@
         <v>1.8679000000000001E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88000</v>
       </c>
@@ -9697,7 +11225,7 @@
         <v>1.8821000000000001E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89000</v>
       </c>
@@ -9717,7 +11245,7 @@
         <v>1.9036000000000001E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90000</v>
       </c>
@@ -9737,7 +11265,7 @@
         <v>1.9393000000000001E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91000</v>
       </c>
@@ -9757,7 +11285,7 @@
         <v>1.9820999999999998E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92000</v>
       </c>
@@ -9777,7 +11305,7 @@
         <v>1.9963999999999999E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93000</v>
       </c>
@@ -9797,7 +11325,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94000</v>
       </c>
@@ -9817,7 +11345,7 @@
         <v>2.0213999999999999E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95000</v>
       </c>
@@ -9837,7 +11365,7 @@
         <v>2.0678999999999999E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96000</v>
       </c>
@@ -9857,7 +11385,7 @@
         <v>2.3036000000000001E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97000</v>
       </c>
@@ -9877,7 +11405,7 @@
         <v>2.3213999999999999E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98000</v>
       </c>
@@ -9897,7 +11425,7 @@
         <v>2.3393000000000001E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99000</v>
       </c>
@@ -9917,7 +11445,7 @@
         <v>2.3106999999999999E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100000</v>
       </c>
@@ -9947,17 +11475,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71C5F1C5-FF90-4A07-A634-21D9F68CF943}">
   <dimension ref="B1:D101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B2" s="3"/>
       <c r="C2" s="1">
         <v>1.75E-3</v>
@@ -9966,7 +11494,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
       <c r="C3" s="1">
         <v>4.8570000000000002E-3</v>
@@ -9975,7 +11503,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" s="1">
         <v>7.6790000000000001E-3</v>
@@ -9984,7 +11512,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" s="1">
         <v>9.1789999999999997E-3</v>
@@ -9993,7 +11521,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="3"/>
       <c r="C6" s="1">
         <v>1.6535999999999999E-2</v>
@@ -10002,7 +11530,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="3"/>
       <c r="C7" s="1">
         <v>1.5285999999999999E-2</v>
@@ -10011,7 +11539,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" s="3"/>
       <c r="C8" s="1">
         <v>1.6607E-2</v>
@@ -10020,7 +11548,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="3"/>
       <c r="C9" s="1">
         <v>2.7286000000000001E-2</v>
@@ -10029,7 +11557,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B10" s="3"/>
       <c r="C10" s="1">
         <v>2.35E-2</v>
@@ -10038,7 +11566,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B11" s="3"/>
       <c r="C11" s="1">
         <v>2.2606999999999999E-2</v>
@@ -10047,7 +11575,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
       <c r="C12" s="1">
         <v>2.6286E-2</v>
@@ -10056,7 +11584,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B13" s="3"/>
       <c r="C13" s="1">
         <v>3.0071000000000001E-2</v>
@@ -10065,7 +11593,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
       <c r="C14" s="1">
         <v>3.1713999999999999E-2</v>
@@ -10074,7 +11602,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B15" s="3"/>
       <c r="C15" s="1">
         <v>4.7750000000000001E-2</v>
@@ -10083,7 +11611,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
       <c r="C16" s="1">
         <v>4.65E-2</v>
@@ -10092,7 +11620,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" s="3"/>
       <c r="C17" s="1">
         <v>4.3570999999999999E-2</v>
@@ -10101,7 +11629,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B18" s="3"/>
       <c r="C18" s="1">
         <v>5.0929000000000002E-2</v>
@@ -10110,7 +11638,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B19" s="3"/>
       <c r="C19" s="1">
         <v>5.1893000000000002E-2</v>
@@ -10119,7 +11647,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" s="3"/>
       <c r="C20" s="1">
         <v>5.0929000000000002E-2</v>
@@ -10128,7 +11656,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B21" s="3"/>
       <c r="C21" s="1">
         <v>5.3107000000000001E-2</v>
@@ -10137,7 +11665,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B22" s="3"/>
       <c r="C22" s="1">
         <v>4.9964000000000001E-2</v>
@@ -10146,7 +11674,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" s="3"/>
       <c r="C23" s="1">
         <v>4.7892999999999998E-2</v>
@@ -10155,7 +11683,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B24" s="3"/>
       <c r="C24" s="1">
         <v>5.7070999999999997E-2</v>
@@ -10164,7 +11692,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B25" s="3"/>
       <c r="C25" s="1">
         <v>5.3749999999999999E-2</v>
@@ -10173,7 +11701,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B26" s="3"/>
       <c r="C26" s="1">
         <v>5.8964000000000003E-2</v>
@@ -10182,7 +11710,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B27" s="3"/>
       <c r="C27" s="1">
         <v>5.7964000000000002E-2</v>
@@ -10191,7 +11719,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B28" s="3"/>
       <c r="C28" s="1">
         <v>6.0463999999999997E-2</v>
@@ -10200,7 +11728,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B29" s="3"/>
       <c r="C29" s="1">
         <v>5.9820999999999999E-2</v>
@@ -10209,7 +11737,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B30" s="3"/>
       <c r="C30" s="1">
         <v>6.7642999999999995E-2</v>
@@ -10218,7 +11746,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B31" s="3"/>
       <c r="C31" s="1">
         <v>6.5785999999999997E-2</v>
@@ -10227,7 +11755,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B32" s="3"/>
       <c r="C32" s="1">
         <v>7.2249999999999995E-2</v>
@@ -10236,7 +11764,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="3"/>
       <c r="C33" s="1">
         <v>7.0357000000000003E-2</v>
@@ -10245,7 +11773,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" s="3"/>
       <c r="C34" s="1">
         <v>7.1570999999999996E-2</v>
@@ -10254,7 +11782,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" s="3"/>
       <c r="C35" s="1">
         <v>7.825E-2</v>
@@ -10263,7 +11791,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B36" s="3"/>
       <c r="C36" s="1">
         <v>8.1429000000000001E-2</v>
@@ -10272,7 +11800,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B37" s="3"/>
       <c r="C37" s="1">
         <v>8.4463999999999997E-2</v>
@@ -10281,7 +11809,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B38" s="3"/>
       <c r="C38" s="1">
         <v>8.1679000000000002E-2</v>
@@ -10290,7 +11818,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B39" s="3"/>
       <c r="C39" s="1">
         <v>8.2750000000000004E-2</v>
@@ -10299,7 +11827,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B40" s="3"/>
       <c r="C40" s="1">
         <v>8.7964000000000001E-2</v>
@@ -10308,7 +11836,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B41" s="3"/>
       <c r="C41" s="1">
         <v>0.10435700000000001</v>
@@ -10317,7 +11845,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B42" s="3"/>
       <c r="C42" s="1">
         <v>0.12725</v>
@@ -10326,7 +11854,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B43" s="3"/>
       <c r="C43" s="1">
         <v>0.14482100000000001</v>
@@ -10335,7 +11863,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B44" s="3"/>
       <c r="C44" s="1">
         <v>0.173036</v>
@@ -10344,7 +11872,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B45" s="3"/>
       <c r="C45" s="1">
         <v>0.12653600000000001</v>
@@ -10353,7 +11881,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B46" s="3"/>
       <c r="C46" s="1">
         <v>0.113357</v>
@@ -10362,7 +11890,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B47" s="3"/>
       <c r="C47" s="1">
         <v>0.125857</v>
@@ -10371,7 +11899,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B48" s="3"/>
       <c r="C48" s="1">
         <v>0.11632099999999999</v>
@@ -10380,7 +11908,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B49" s="3"/>
       <c r="C49" s="1">
         <v>0.121321</v>
@@ -10389,7 +11917,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B50" s="3"/>
       <c r="C50" s="1">
         <v>0.120536</v>
@@ -10398,7 +11926,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B51" s="3"/>
       <c r="C51" s="1">
         <v>0.13007099999999999</v>
@@ -10407,7 +11935,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B52" s="3"/>
       <c r="C52" s="1">
         <v>0.131857</v>
@@ -10416,7 +11944,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B53" s="3"/>
       <c r="C53" s="1">
         <v>0.128357</v>
@@ -10425,7 +11953,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B54" s="3"/>
       <c r="C54" s="1">
         <v>0.13157099999999999</v>
@@ -10434,7 +11962,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B55" s="3"/>
       <c r="C55" s="1">
         <v>0.14135700000000001</v>
@@ -10443,7 +11971,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B56" s="3"/>
       <c r="C56" s="1">
         <v>0.12989300000000001</v>
@@ -10452,7 +11980,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B57" s="3"/>
       <c r="C57" s="1">
         <v>0.133357</v>
@@ -10461,7 +11989,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B58" s="3"/>
       <c r="C58" s="1">
         <v>0.14599999999999999</v>
@@ -10470,7 +11998,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B59" s="3"/>
       <c r="C59" s="1">
         <v>0.138429</v>
@@ -10479,7 +12007,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B60" s="3"/>
       <c r="C60" s="1">
         <v>0.14264299999999999</v>
@@ -10488,7 +12016,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B61" s="3"/>
       <c r="C61" s="1">
         <v>0.14246400000000001</v>
@@ -10497,7 +12025,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B62" s="3"/>
       <c r="C62" s="1">
         <v>0.146036</v>
@@ -10506,7 +12034,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B63" s="3"/>
       <c r="C63" s="1">
         <v>0.15024999999999999</v>
@@ -10515,7 +12043,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B64" s="3"/>
       <c r="C64" s="1">
         <v>0.146179</v>
@@ -10524,7 +12052,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B65" s="3"/>
       <c r="C65" s="1">
         <v>0.16089300000000001</v>
@@ -10533,7 +12061,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B66" s="3"/>
       <c r="C66" s="1">
         <v>0.15332100000000001</v>
@@ -10542,7 +12070,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B67" s="3"/>
       <c r="C67" s="1">
         <v>0.16017899999999999</v>
@@ -10551,7 +12079,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B68" s="3"/>
       <c r="C68" s="1">
         <v>0.162714</v>
@@ -10560,7 +12088,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B69" s="3"/>
       <c r="C69" s="1">
         <v>0.16764299999999999</v>
@@ -10569,7 +12097,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B70" s="3"/>
       <c r="C70" s="1">
         <v>0.178893</v>
@@ -10578,7 +12106,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B71" s="3"/>
       <c r="C71" s="1">
         <v>0.17121400000000001</v>
@@ -10587,7 +12115,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B72" s="3"/>
       <c r="C72" s="1">
         <v>0.172679</v>
@@ -10596,7 +12124,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="73" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B73" s="3"/>
       <c r="C73" s="1">
         <v>0.17689299999999999</v>
@@ -10605,7 +12133,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="74" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B74" s="3"/>
       <c r="C74" s="1">
         <v>0.17371400000000001</v>
@@ -10614,7 +12142,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="75" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B75" s="3"/>
       <c r="C75" s="1">
         <v>0.18521399999999999</v>
@@ -10623,7 +12151,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="76" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B76" s="3"/>
       <c r="C76" s="1">
         <v>0.187893</v>
@@ -10632,7 +12160,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="77" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B77" s="3"/>
       <c r="C77" s="1">
         <v>0.18807099999999999</v>
@@ -10641,7 +12169,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B78" s="3"/>
       <c r="C78" s="1">
         <v>0.18864300000000001</v>
@@ -10650,7 +12178,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="79" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B79" s="3"/>
       <c r="C79" s="1">
         <v>0.19017899999999999</v>
@@ -10659,7 +12187,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="80" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B80" s="3"/>
       <c r="C80" s="1">
         <v>0.200179</v>
@@ -10668,7 +12196,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="81" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B81" s="3"/>
       <c r="C81" s="1">
         <v>0.20003599999999999</v>
@@ -10677,7 +12205,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B82" s="3"/>
       <c r="C82" s="1">
         <v>0.214393</v>
@@ -10686,7 +12214,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="83" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B83" s="3"/>
       <c r="C83" s="1">
         <v>0.19557099999999999</v>
@@ -10695,7 +12223,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="84" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B84" s="3"/>
       <c r="C84" s="1">
         <v>0.201464</v>
@@ -10704,7 +12232,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="85" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B85" s="3"/>
       <c r="C85" s="1">
         <v>0.20571400000000001</v>
@@ -10713,7 +12241,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="86" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B86" s="3"/>
       <c r="C86" s="1">
         <v>0.21174999999999999</v>
@@ -10722,7 +12250,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="87" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B87" s="3"/>
       <c r="C87" s="1">
         <v>0.21099999999999999</v>
@@ -10731,7 +12259,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="88" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B88" s="3"/>
       <c r="C88" s="1">
         <v>0.22382099999999999</v>
@@ -10740,7 +12268,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="89" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B89" s="3"/>
       <c r="C89" s="1">
         <v>0.226607</v>
@@ -10749,7 +12277,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="90" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B90" s="3"/>
       <c r="C90" s="1">
         <v>0.22267899999999999</v>
@@ -10758,7 +12286,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="91" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B91" s="3"/>
       <c r="C91" s="1">
         <v>0.21775</v>
@@ -10767,7 +12295,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="92" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B92" s="3"/>
       <c r="C92" s="1">
         <v>0.246286</v>
@@ -10776,7 +12304,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="93" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B93" s="3"/>
       <c r="C93" s="1">
         <v>0.22850000000000001</v>
@@ -10785,7 +12313,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="94" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B94" s="3"/>
       <c r="C94" s="1">
         <v>0.22675000000000001</v>
@@ -10794,7 +12322,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="95" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B95" s="3"/>
       <c r="C95" s="1">
         <v>0.22978599999999999</v>
@@ -10803,7 +12331,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="96" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B96" s="3"/>
       <c r="C96" s="1">
         <v>0.23524999999999999</v>
@@ -10812,7 +12340,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="97" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B97" s="3"/>
       <c r="C97" s="1">
         <v>0.23639299999999999</v>
@@ -10821,7 +12349,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="98" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B98" s="3"/>
       <c r="C98" s="1">
         <v>0.247</v>
@@ -10830,7 +12358,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="99" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B99" s="3"/>
       <c r="C99" s="1">
         <v>0.25024999999999997</v>
@@ -10839,7 +12367,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="100" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B100" s="3"/>
       <c r="C100" s="1">
         <v>0.242286</v>
@@ -10848,7 +12376,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="101" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B101" s="3"/>
       <c r="C101" s="1">
         <v>0.251357</v>
@@ -10864,11 +12392,824 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A41020-5021-4401-B847-11EF1E1FA1B3}">
+  <dimension ref="A1:F100"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>1.8929999999999999E-3</v>
+      </c>
+      <c r="B1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>3.679E-3</v>
+      </c>
+      <c r="B2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>6.6429999999999996E-3</v>
+      </c>
+      <c r="B3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>8.6429999999999996E-3</v>
+      </c>
+      <c r="B4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1.1535999999999999E-2</v>
+      </c>
+      <c r="B5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1.3036000000000001E-2</v>
+      </c>
+      <c r="B6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1.5070999999999999E-2</v>
+      </c>
+      <c r="B7">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1.6607E-2</v>
+      </c>
+      <c r="B8">
+        <v>80</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1.8856999999999999E-2</v>
+      </c>
+      <c r="B9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>2.0929E-2</v>
+      </c>
+      <c r="B10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>2.2464000000000001E-2</v>
+      </c>
+      <c r="B11">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>2.4785999999999999E-2</v>
+      </c>
+      <c r="B12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>2.6356999999999998E-2</v>
+      </c>
+      <c r="B13">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>2.9642999999999999E-2</v>
+      </c>
+      <c r="B14">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>3.0536000000000001E-2</v>
+      </c>
+      <c r="B15">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>3.2679E-2</v>
+      </c>
+      <c r="B16">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>3.4393E-2</v>
+      </c>
+      <c r="B17">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>3.6499999999999998E-2</v>
+      </c>
+      <c r="B18">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>3.875E-2</v>
+      </c>
+      <c r="B19">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>4.0429E-2</v>
+      </c>
+      <c r="B20">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>4.2535999999999997E-2</v>
+      </c>
+      <c r="B21">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>4.4357000000000001E-2</v>
+      </c>
+      <c r="B22">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>4.65E-2</v>
+      </c>
+      <c r="B23">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>4.7821000000000002E-2</v>
+      </c>
+      <c r="B24">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>5.0535999999999998E-2</v>
+      </c>
+      <c r="B25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>5.3499999999999999E-2</v>
+      </c>
+      <c r="B26">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>5.4642999999999997E-2</v>
+      </c>
+      <c r="B27">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>5.6929E-2</v>
+      </c>
+      <c r="B28">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>5.8820999999999998E-2</v>
+      </c>
+      <c r="B29">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>5.9429000000000003E-2</v>
+      </c>
+      <c r="B30">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>6.1463999999999998E-2</v>
+      </c>
+      <c r="B31">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>6.4429E-2</v>
+      </c>
+      <c r="B32">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>6.9142999999999996E-2</v>
+      </c>
+      <c r="B33">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>6.9892999999999997E-2</v>
+      </c>
+      <c r="B34">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>7.3214000000000001E-2</v>
+      </c>
+      <c r="B35">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>7.2892999999999999E-2</v>
+      </c>
+      <c r="B36">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>7.4714000000000003E-2</v>
+      </c>
+      <c r="B37">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>7.5320999999999999E-2</v>
+      </c>
+      <c r="B38">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>7.6356999999999994E-2</v>
+      </c>
+      <c r="B39">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>7.8214000000000006E-2</v>
+      </c>
+      <c r="B40">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>8.0321000000000004E-2</v>
+      </c>
+      <c r="B41">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>8.1963999999999995E-2</v>
+      </c>
+      <c r="B42">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>8.4036E-2</v>
+      </c>
+      <c r="B43">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>8.5892999999999997E-2</v>
+      </c>
+      <c r="B44">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>8.8070999999999997E-2</v>
+      </c>
+      <c r="B45">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>8.9820999999999998E-2</v>
+      </c>
+      <c r="B46">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>9.1786000000000006E-2</v>
+      </c>
+      <c r="B47">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>9.3606999999999996E-2</v>
+      </c>
+      <c r="B48">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>9.5713999999999994E-2</v>
+      </c>
+      <c r="B49">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>9.7392999999999993E-2</v>
+      </c>
+      <c r="B50">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>9.9500000000000005E-2</v>
+      </c>
+      <c r="B51">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>0.101393</v>
+      </c>
+      <c r="B52">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>0.103214</v>
+      </c>
+      <c r="B53">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>0.105214</v>
+      </c>
+      <c r="B54">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>0.10685699999999999</v>
+      </c>
+      <c r="B55">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>0.109071</v>
+      </c>
+      <c r="B56">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>0.110821</v>
+      </c>
+      <c r="B57">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>0.113714</v>
+      </c>
+      <c r="B58">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="B59">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>0.116893</v>
+      </c>
+      <c r="B60">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>0.118571</v>
+      </c>
+      <c r="B61">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>0.120321</v>
+      </c>
+      <c r="B62">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>0.122321</v>
+      </c>
+      <c r="B63">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>0.12428599999999999</v>
+      </c>
+      <c r="B64">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>0.12625</v>
+      </c>
+      <c r="B65">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>0.12853600000000001</v>
+      </c>
+      <c r="B66">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>0.13017899999999999</v>
+      </c>
+      <c r="B67">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>0.13339300000000001</v>
+      </c>
+      <c r="B68">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>0.133857</v>
+      </c>
+      <c r="B69">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>0.135821</v>
+      </c>
+      <c r="B70">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>0.13778599999999999</v>
+      </c>
+      <c r="B71">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>0.13964299999999999</v>
+      </c>
+      <c r="B72">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>0.14146400000000001</v>
+      </c>
+      <c r="B73">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>0.14349999999999999</v>
+      </c>
+      <c r="B74">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>0.146786</v>
+      </c>
+      <c r="B75">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>0.15082100000000001</v>
+      </c>
+      <c r="B76">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>0.14907100000000001</v>
+      </c>
+      <c r="B77">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>0.15142900000000001</v>
+      </c>
+      <c r="B78">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>0.15296399999999999</v>
+      </c>
+      <c r="B79">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>0.155</v>
+      </c>
+      <c r="B80">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>0.156857</v>
+      </c>
+      <c r="B81">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>0.15882099999999999</v>
+      </c>
+      <c r="B82">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>0.16042899999999999</v>
+      </c>
+      <c r="B83">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>0.16275000000000001</v>
+      </c>
+      <c r="B84">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>0.165571</v>
+      </c>
+      <c r="B85">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>0.16650000000000001</v>
+      </c>
+      <c r="B86">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>0.16839299999999999</v>
+      </c>
+      <c r="B87">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>0.16989299999999999</v>
+      </c>
+      <c r="B88">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>0.17446400000000001</v>
+      </c>
+      <c r="B89">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>0.17574999999999999</v>
+      </c>
+      <c r="B90">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>0.17589299999999999</v>
+      </c>
+      <c r="B91">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>0.17760699999999999</v>
+      </c>
+      <c r="B92">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>0.17982100000000001</v>
+      </c>
+      <c r="B93">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>0.18132100000000001</v>
+      </c>
+      <c r="B94">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>0.183786</v>
+      </c>
+      <c r="B95">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>0.18496399999999999</v>
+      </c>
+      <c r="B96">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>0.18732099999999999</v>
+      </c>
+      <c r="B97">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>0.18907099999999999</v>
+      </c>
+      <c r="B98">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>0.19078600000000001</v>
+      </c>
+      <c r="B99">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>0.193214</v>
+      </c>
+      <c r="B100">
+        <v>1000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA555A06-F6FC-4E68-BD29-AF88BB5D3BB8}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -10876,7 +13217,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
@@ -10884,7 +13225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3</v>
       </c>
@@ -10892,7 +13233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>4</v>
       </c>
@@ -10900,7 +13241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5</v>
       </c>
@@ -10908,7 +13249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>6</v>
       </c>
@@ -10916,7 +13257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>7</v>
       </c>
@@ -10924,7 +13265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>8</v>
       </c>
@@ -10932,7 +13273,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>9</v>
       </c>
@@ -10940,7 +13281,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>10</v>
       </c>
@@ -10948,7 +13289,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>11</v>
       </c>
@@ -10956,7 +13297,7 @@
         <v>3.5449999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>12</v>
       </c>
@@ -10964,7 +13305,7 @@
         <v>28.648</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>13</v>
       </c>
@@ -10972,7 +13313,7 @@
         <v>1053.664</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>14</v>
       </c>
@@ -10983,15 +13324,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9726635B-42D9-42C4-A029-47F7C2CBEB73}">
   <dimension ref="A2:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -11002,7 +13343,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>10</v>
       </c>
@@ -11013,7 +13354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>20</v>
       </c>
@@ -11024,7 +13365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>30</v>
       </c>
@@ -11035,7 +13376,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>40</v>
       </c>
@@ -11046,7 +13387,7 @@
         <v>1.6679999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>50</v>
       </c>
